--- a/Luban/DataTables/Datas/test.demo.xlsx
+++ b/Luban/DataTables/Datas/test.demo.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -41,10 +42,10 @@
     <t>desc</t>
   </si>
   <si>
-    <t>*prop_count</t>
-  </si>
-  <si>
-    <t>*ttest</t>
+    <t>prop_count#format=lite</t>
+  </si>
+  <si>
+    <t>ttest#format=lite</t>
   </si>
   <si>
     <t>##type</t>
@@ -56,7 +57,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>list,int</t>
+    <t>(list#sep,),int</t>
   </si>
   <si>
     <t>map,int,(CostDetail#sep=,)</t>
@@ -65,9 +66,6 @@
     <t>##group</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>c</t>
   </si>
   <si>
@@ -83,19 +81,28 @@
     <t>个数</t>
   </si>
   <si>
-    <t>道具1</t>
-  </si>
-  <si>
-    <t>描述1</t>
-  </si>
-  <si>
-    <t>50,30</t>
-  </si>
-  <si>
-    <t>道具2</t>
-  </si>
-  <si>
-    <t>描述222</t>
+    <t>ITEM0</t>
+  </si>
+  <si>
+    <t>sss</t>
+  </si>
+  <si>
+    <t>房间|成就</t>
+  </si>
+  <si>
+    <t>{1,2,3,4}</t>
+  </si>
+  <si>
+    <t>{{1,{50,30}},{2,{50,30}}}</t>
+  </si>
+  <si>
+    <t>ddd</t>
+  </si>
+  <si>
+    <t>春节</t>
+  </si>
+  <si>
+    <t>{{1,{50,30}}}</t>
   </si>
 </sst>
 </file>
@@ -716,7 +723,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1037,10 +1044,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="5" max="5" width="28.125" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1094,36 +1103,32 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3"/>
+        <v>12</v>
+      </c>
       <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5">
-        <v>1001</v>
+      <c r="B5" t="s">
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -1131,119 +1136,158 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="E5" t="s">
         <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="E6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>20</v>
       </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="E10">
-        <v>60</v>
-      </c>
-      <c r="F10">
-        <v>6</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11">
-        <v>1002</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="E12">
-        <v>90</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="E13">
-        <v>80</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13" t="s">
-        <v>20</v>
+      <c r="F6" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="6"/>
+  <cols>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="28.125" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="22.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" customFormat="1" spans="1:7">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:7">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:7">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:7">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>